--- a/public/exports-with-coowners/29189129.xlsx
+++ b/public/exports-with-coowners/29189129.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558062</t>
+          <t xml:space="preserve">311558064</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">

--- a/public/exports-with-coowners/29189129.xlsx
+++ b/public/exports-with-coowners/29189129.xlsx
@@ -12214,7 +12214,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558064</t>
+          <t xml:space="preserve">311558062</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922583</t>
+          <t xml:space="preserve">311926361</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-17</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
